--- a/publication_ressources_omees/geoflow_entities/entities_metadata_only.xlsx
+++ b/publication_ressources_omees/geoflow_entities/entities_metadata_only.xlsx
@@ -548,7 +548,7 @@
 thumbnail:arbocarto@https://static.cirad.fr/sites/www.arbocarto.fr/images/logo.svg</t>
   </si>
   <si>
-    <t xml:space="preserve">omees_softaware_sustainlight</t>
+    <t xml:space="preserve">omees_software_sustainlight</t>
   </si>
   <si>
     <t xml:space="preserve">title: SustainLight : Outil d'aide à la définition de la trame noire</t>
@@ -800,7 +800,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -867,10 +867,6 @@
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1139,7 +1135,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="13" min="13" style="1" width="29.91"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="14" min="14" style="1" width="11.85"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="15" min="15" style="2" width="63"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="0" width="31.71"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="16" min="16" style="1" width="31.71"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="24.6" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -1623,7 +1619,6 @@
       <c r="M13" s="8" t="s">
         <v>107</v>
       </c>
-      <c r="P13" s="1"/>
     </row>
     <row r="14" customFormat="false" ht="95.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="11" t="s">
@@ -1777,7 +1772,7 @@
       <c r="I18" s="13" t="s">
         <v>140</v>
       </c>
-      <c r="L18" s="17" t="s">
+      <c r="L18" s="9" t="s">
         <v>141</v>
       </c>
       <c r="M18" s="8" t="s">
@@ -1849,11 +1844,11 @@
     <hyperlink ref="L8" r:id="rId1" display="http:website[Catalogue de données géospatiales EEA]@https://sdi.eea.europa.eu/catalogue/_&#10;http:website[European Environment Agency]@https://www.eea.europa.eu/_&#10;http:website[API catalogue]@https://sdi.eea.europa.eu/catalogue/_&#10;thumbnail:copernicus@https://www.copernicus.eu/sites/default/files/styles/image_img_fluid/public/images/media/low/295955-Copernicus_logo_node_full_image_2.jpg"/>
     <hyperlink ref="L13" r:id="rId2" display="http:website[Entrepôt de Données de Santé eDOL]@https://www.chu-montpellier.fr/fr/plateformes-recherche/eds_&#10;http:website[CHU de Montpellier]@https://www.chu-montpellier.fr/_&#10;thumbnail:chu-mtp@https://www.chu-montpellier.fr/fileadmin/Minisites/principal/logo.svg"/>
     <hyperlink ref="E17" r:id="rId3" display="PointOfContact:olivier.gimenez@cefe.cnrs.fr"/>
-    <hyperlink ref="L17" r:id="rId4" display="omees_dataset_datanat_lunaret@https"/>
-    <hyperlink ref="L18" r:id="rId5" display="omees_dataset_datanat_lunaret@https"/>
-    <hyperlink ref="L19" r:id="rId6" display="omees_dataset_datanat_lunaret@https"/>
+    <hyperlink ref="L17" r:id="rId4" display="http:website[Site objectif Lez]@https://objectif-lez.netlify.app/_&#10;parent:omees_dataset_datanat_lunaret@https://geodata.inrae.fr/geonetwork/OMEES/datahub/reuse/omees_dataset_datanat_lunaret"/>
+    <hyperlink ref="L18" r:id="rId5" display="http:website[Carte OpenStreetMap]@https://umap.openstreetmap.fr/fr/map/ev-biod-lavalette_1218144#15/43.646929/3.875299_&#10;parent:omees_dataset_datanat_lunaret@https://geodata.inrae.fr/geonetwork/OMEES/datahub/reuse/omees_dataset_datanat_lunaret"/>
+    <hyperlink ref="L19" r:id="rId6" display="http:website[Visualiseur SINP Montpellier]@https://sinp-occitanie.fr/atlas/commune/34172_&#10;parent:omees_dataset_datanat_lunaret@https://geodata.inrae.fr/geonetwork/OMEES/datahub/reuse/omees_dataset_datanat_lunaret"/>
     <hyperlink ref="E20" r:id="rId7" display="PointOfContact:olivier.gimenez@cefe.cnrs.fr"/>
-    <hyperlink ref="L20" r:id="rId8" display="omees_dataset_datanat_lunaret@https"/>
+    <hyperlink ref="L20" r:id="rId8" display="parent:omees_dataset_datanat_lunaret@https://geodata.inrae.fr/geonetwork/OMEES/datahub/reuse/omees_dataset_datanat_lunaret"/>
   </hyperlinks>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.700694444444445" right="0.700694444444445" top="0.752083333333333" bottom="0.752083333333333" header="0.511811023622047" footer="0.511811023622047"/>
